--- a/JsonConverter/ExcelFiles/CatInfoData.xlsx
+++ b/JsonConverter/ExcelFiles/CatInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0870FE7-39D8-4B62-936D-4A0275A0AEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FDD799-D452-42DF-A24D-904549FBE286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="2520" windowWidth="26580" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28995" yWindow="2985" windowWidth="22890" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cat" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -105,6 +105,18 @@
   </si>
   <si>
     <t>고냥이 사전 아이콘 이미지 경로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/TestIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/TestIcon2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/TestIcon3</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -564,7 +576,9 @@
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -576,6 +590,9 @@
       <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="F5" s="12" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
@@ -586,6 +603,9 @@
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/CatInfoData.xlsx
+++ b/JsonConverter/ExcelFiles/CatInfoData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FDD799-D452-42DF-A24D-904549FBE286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B3D9EC-E994-4153-AA3C-006310559776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28995" yWindow="2985" windowWidth="22890" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -117,6 +117,18 @@
   </si>
   <si>
     <t>UI/CatIcon/TestIcon3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이 등장 가중치</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CatAppearanceWeight</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -252,7 +264,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -279,6 +291,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -497,7 +510,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
@@ -510,7 +523,7 @@
     <col min="8" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,8 +538,11 @@
       <c r="F1" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="12.75">
+      <c r="G1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -545,8 +561,11 @@
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="G2" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -565,8 +584,11 @@
       <c r="F3" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G3" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -579,8 +601,11 @@
       <c r="F4" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G4" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -593,8 +618,11 @@
       <c r="F5" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G5" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -607,53 +635,56 @@
       <c r="F6" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="G6" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>

--- a/JsonConverter/ExcelFiles/CatInfoData.xlsx
+++ b/JsonConverter/ExcelFiles/CatInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B3D9EC-E994-4153-AA3C-006310559776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CC1310-FE7B-49B8-A9DD-9B701F2B2CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28995" yWindow="2985" windowWidth="22890" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34620" yWindow="1725" windowWidth="21480" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cat" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -96,14 +96,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>고냥이 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>효과 수치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>고냥이 사전 아이콘 이미지 경로</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -129,6 +121,29 @@
   </si>
   <si>
     <t>CatAppearanceWeight</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multiplies</t>
+  </si>
+  <si>
+    <t>Multiplies</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">효과 수치
+Multiplies : 0.5미만
+Add : 10 이하
+</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고냥이 효과
+Multiplies, Add</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -264,7 +279,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -292,6 +307,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -515,9 +533,9 @@
   <cols>
     <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17" style="3" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" style="3" customWidth="1"/>
     <col min="7" max="7" width="20" style="3" customWidth="1"/>
     <col min="8" max="16384" width="12.5703125" style="3"/>
@@ -529,17 +547,17 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="12.75">
@@ -562,7 +580,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="11" customFormat="1" ht="15.75" customHeight="1">
@@ -585,7 +603,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
@@ -598,8 +616,14 @@
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
       <c r="F4" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>1000</v>
@@ -615,8 +639,14 @@
       <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="D5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.1</v>
+      </c>
       <c r="F5" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>10</v>
@@ -632,8 +662,14 @@
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
       <c r="F6" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3">
         <v>10</v>
@@ -643,128 +679,144 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
+      <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
+      <c r="D9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
+      <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D22" s="14"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
     </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
     </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
     </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
     </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1751,6 +1803,14 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D26" xr:uid="{D9E36C4A-5157-4DFC-8E73-81C258906CB0}">
+      <formula1>"Multiplies,Add"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Multiplies : 0.5미만_x000a_Add : 10 이하" sqref="E4:E33" xr:uid="{E1A75498-55C4-41BC-96CC-BEE116E57425}">
+      <formula1>OR(AND(D4="Multiplies",E4&gt;=0,E4&lt;0.5),AND(D4="Add",E4&gt;=0,E4&lt;=10))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/CatInfoData.xlsx
+++ b/JsonConverter/ExcelFiles/CatInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CC1310-FE7B-49B8-A9DD-9B701F2B2CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52F727F-851E-420A-B181-35CD6BBC513F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34620" yWindow="1725" windowWidth="21480" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29190" yWindow="1710" windowWidth="25110" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cat" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -52,30 +52,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>특별 고양이 1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>특별 고냥이2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>특별 고양이1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>특별 고냥이 2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 고양이</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 고양이다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -101,14 +77,6 @@
   </si>
   <si>
     <t>UI/CatIcon/TestIcon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI/CatIcon/TestIcon2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI/CatIcon/TestIcon3</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -144,6 +112,128 @@
   <si>
     <t>고냥이 효과
 Multiplies, Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">특수 고양이 입 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>Addressable</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 고양이 몸 Addressable</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">특수 고양이 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>Addressable</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialCatBody</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialCatEye</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialCatMouth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 고냥이다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금 고냥이다.
+이 고냥이는 금으로 되어 있으며 보았다는 경험만으로 돈의 핵심을 깨닫게 해준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Gold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Gold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Gold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/GoldCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식을 하는 고냥이다.
+이 고냥이는 주식의 핵심을 깨달았다. 목격 사실만으로 돈을 추가로 벌 수 있는 방법을 깨닫는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Stock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Stock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Stock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/StockCatIcon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -151,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -189,6 +279,19 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -279,7 +382,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -309,6 +412,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,7 +635,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
@@ -541,26 +648,35 @@
     <col min="8" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="15" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="12.75">
+    <row r="2" spans="1:10" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -571,19 +687,28 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="11" customFormat="1" ht="15.75" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -594,142 +719,178 @@
         <v>1</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+        <v>18</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>9</v>
+        <v>31</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E5" s="3">
         <v>0.1</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G5" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="14"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="14"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="14"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="14"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="14"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="14"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>

--- a/JsonConverter/ExcelFiles/CatInfoData.xlsx
+++ b/JsonConverter/ExcelFiles/CatInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52F727F-851E-420A-B181-35CD6BBC513F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63638762-204D-403D-8626-5D59117557B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29190" yWindow="1710" windowWidth="25110" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32445" yWindow="2490" windowWidth="25110" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cat" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -45,10 +45,6 @@
   </si>
   <si>
     <t>Cat_Special_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cat_Special_02</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -179,23 +175,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>황금 고냥이</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>일반 고냥이</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>일반 고냥이다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>황금 고냥이다.
-이 고냥이는 금으로 되어 있으며 보았다는 경험만으로 돈의 핵심을 깨닫게 해준다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Cat_Material_Body_Gold</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -216,24 +199,185 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>Cat_Material_Body_Stock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Stock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Stock</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/StockCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Special_03</t>
+  </si>
+  <si>
+    <t>경찰 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Police</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Police</t>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Police</t>
+  </si>
+  <si>
+    <t>UI/CatIcon/HealthCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Special_04</t>
+  </si>
+  <si>
+    <t>운동 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Health</t>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Health</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Health</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/PoliceCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Special_02</t>
+  </si>
+  <si>
+    <t>Cat_Special_05</t>
+  </si>
+  <si>
+    <t>Cat_Special_06</t>
+  </si>
+  <si>
+    <t>은 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>동 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 고냥이다
+수집효과 : 없음</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>금 고냥이다.
+이 고냥이는 금으로 되어 있으며 보았다는 경험만으로 돈의 핵심을 매우 깨닫게 해준다.
+수집효과 : 수입률 + 45%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>은 고냥이다.
+이 고냥이는 은으로 되어 있으며 보았다는 경험만으로 돈의 핵심을 깨닫게 해준다.
+수집효과 : 수입률 + 20%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>동 고냥이다.
+이 고냥이는 동으로 되어 있으며 보았다는 경험만으로 돈의 핵심을 살짝 깨닫게 해준다.
+수집효과 : 수입률 + 10%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>경찰 고냥이다.
+경찰 고냥이의 존재로 인해 횡력하는 돈들을 막을 수 있게 되었다.
+수집효과 : 수입률 + 10%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>주식을 하는 고냥이다.
-이 고냥이는 주식의 핵심을 깨달았다. 목격 사실만으로 돈을 추가로 벌 수 있는 방법을 깨닫는다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cat_Material_Body_Stock</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cat_Material_Eye_Stock</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cat_Material_Mouth_Stock</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI/CatIcon/StockCatIcon</t>
+이 고냥이는 주식의 핵심을 깨달았다. 목격 사실만으로 돈을 추가로 벌 수 있는 방법을 깨닫는다.
+수집효과 : 기본수입 + 5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Bronze</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Silver</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Bronze</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Silver</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Silver</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Bronze</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Special_07</t>
+  </si>
+  <si>
+    <t>Cat_Material_Body_Heisenberg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Eye_Heisenberg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat_Material_Mouth_Heisenberg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>약사 고냥이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>약을 제조할 수 있는 고냥이다.
+고냥이 마을의 의료관광에 도움을 주고 있다.
+수집효과 : 기본수입 + 1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>운동을 좋아하는 고냥이다.
+운동 관광을 위해 회원권을 끊었다.
+수집효과 : 기본수입 + 1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/HeigenbergCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/SilverCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/BronzeCatIcon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +526,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -415,6 +559,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -635,7 +782,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J1002"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
@@ -655,25 +802,25 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75">
@@ -687,25 +834,25 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
@@ -719,25 +866,25 @@
         <v>1</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
@@ -745,31 +892,31 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
@@ -777,129 +924,259 @@
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>35</v>
-      </c>
       <c r="I5" s="14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3">
         <v>10</v>
       </c>
       <c r="H6" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="3">
+        <v>50</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="3">
+        <v>10</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="C9" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="3">
+        <v>10</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="I9" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="14"/>
+      <c r="J9" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="14"/>
+      <c r="A10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3">
+        <v>10</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="14"/>
+      <c r="A11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="3">
+        <v>10</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="14"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
       <c r="D13" s="14"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
       <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="14"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1">
@@ -936,11 +1213,13 @@
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
@@ -948,14 +1227,14 @@
       <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
@@ -978,14 +1257,14 @@
       <c r="C31" s="8"/>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
@@ -997,8 +1276,16 @@
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+    </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
@@ -1962,13 +2249,15 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D26" xr:uid="{D9E36C4A-5157-4DFC-8E73-81C258906CB0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D28" xr:uid="{D9E36C4A-5157-4DFC-8E73-81C258906CB0}">
       <formula1>"Multiplies,Add"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Multiplies : 0.5미만_x000a_Add : 10 이하" sqref="E4:E33" xr:uid="{E1A75498-55C4-41BC-96CC-BEE116E57425}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Multiplies : 0.5미만_x000a_Add : 10 이하" sqref="E4:E35" xr:uid="{E1A75498-55C4-41BC-96CC-BEE116E57425}">
       <formula1>OR(AND(D4="Multiplies",E4&gt;=0,E4&lt;0.5),AND(D4="Add",E4&gt;=0,E4&lt;=10))</formula1>
     </dataValidation>
   </dataValidations>

--- a/JsonConverter/ExcelFiles/CatInfoData.xlsx
+++ b/JsonConverter/ExcelFiles/CatInfoData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63638762-204D-403D-8626-5D59117557B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5418D2CD-5D7C-4C25-BC07-2C03348C94B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32445" yWindow="2490" windowWidth="25110" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,10 +69,6 @@
   </si>
   <si>
     <t>고냥이 사전 아이콘 이미지 경로</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI/CatIcon/TestIcon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -378,6 +374,10 @@
   </si>
   <si>
     <t>UI/CatIcon/BronzeCatIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/CatIcon/CommonCatIcon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -802,25 +802,25 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>25</v>
-      </c>
       <c r="J1" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75">
@@ -843,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>8</v>
@@ -875,16 +875,16 @@
         <v>12</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
@@ -892,31 +892,31 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="G4" s="3">
         <v>1000</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
@@ -924,223 +924,223 @@
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="3">
         <v>0.45</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
       </c>
       <c r="H5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3">
         <v>0.2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3">
         <v>10</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>67</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3">
         <v>0.1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3">
         <v>50</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3">
         <v>5</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="3">
         <v>10</v>
       </c>
       <c r="H8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="J8" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="3">
         <v>0.1</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3">
         <v>10</v>
       </c>
       <c r="H9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3">
         <v>10</v>
       </c>
       <c r="H10" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>49</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>75</v>
-      </c>
       <c r="D11" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3">
         <v>10</v>
       </c>
       <c r="H11" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="J11" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
